--- a/02_Zero_Shot/outputs/LLM/GPT/RESULT_f-droid_gpt-4o_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/LLM/GPT/RESULT_f-droid_gpt-4o_zeroshot.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14469,7 +14469,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="C1063" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19433,7 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -19858,7 +19858,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20487,7 +20487,7 @@
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -21320,7 +21320,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -21354,7 +21354,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -21371,7 +21371,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -21405,7 +21405,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -22561,7 +22561,7 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24285,7 +24285,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24319,7 +24319,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24965,7 +24965,7 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -27261,7 +27261,7 @@
       </c>
       <c r="C1578" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="C1643" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -28383,7 +28383,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -28400,7 +28400,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="C1736" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -30049,7 +30049,7 @@
       </c>
       <c r="C1742" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31137,7 @@
       </c>
       <c r="C1806" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -32089,7 +32089,7 @@
       </c>
       <c r="C1862" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -33313,7 +33313,7 @@
       </c>
       <c r="C1934" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -33908,7 +33908,7 @@
       </c>
       <c r="C1969" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -37682,7 +37682,7 @@
       </c>
       <c r="C2191" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="C2238" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40028,7 +40028,7 @@
       </c>
       <c r="C2329" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -40351,7 +40351,7 @@
       </c>
       <c r="C2348" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40368,7 +40368,7 @@
       </c>
       <c r="C2349" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40385,7 +40385,7 @@
       </c>
       <c r="C2350" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40555,7 +40555,7 @@
       </c>
       <c r="C2360" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40572,7 +40572,7 @@
       </c>
       <c r="C2361" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40589,7 +40589,7 @@
       </c>
       <c r="C2362" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40606,7 +40606,7 @@
       </c>
       <c r="C2363" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -40895,7 +40895,7 @@
       </c>
       <c r="C2380" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -41184,7 +41184,7 @@
       </c>
       <c r="C2397" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -41473,7 +41473,7 @@
       </c>
       <c r="C2414" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -41490,7 +41490,7 @@
       </c>
       <c r="C2415" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -41507,7 +41507,7 @@
       </c>
       <c r="C2416" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -42306,7 +42306,7 @@
       </c>
       <c r="C2463" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -42901,7 +42901,7 @@
       </c>
       <c r="C2498" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -42918,7 +42918,7 @@
       </c>
       <c r="C2499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -42935,7 +42935,7 @@
       </c>
       <c r="C2500" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43020,7 +43020,7 @@
       </c>
       <c r="C2505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43615,7 +43615,7 @@
       </c>
       <c r="C2540" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43632,7 +43632,7 @@
       </c>
       <c r="C2541" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43649,7 @@
       </c>
       <c r="C2542" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -43700,7 +43700,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44023,7 +44023,7 @@
       </c>
       <c r="C2564" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44040,7 +44040,7 @@
       </c>
       <c r="C2565" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44057,7 +44057,7 @@
       </c>
       <c r="C2566" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44329,7 +44329,7 @@
       </c>
       <c r="C2582" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44346,7 +44346,7 @@
       </c>
       <c r="C2583" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44363,7 +44363,7 @@
       </c>
       <c r="C2584" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44380,7 +44380,7 @@
       </c>
       <c r="C2585" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44397,7 +44397,7 @@
       </c>
       <c r="C2586" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -44414,7 +44414,7 @@
       </c>
       <c r="C2587" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -45655,7 +45655,7 @@
       </c>
       <c r="C2660" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -45672,7 +45672,7 @@
       </c>
       <c r="C2661" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C2684" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46097,7 +46097,7 @@
       </c>
       <c r="C2686" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46165,7 +46165,7 @@
       </c>
       <c r="C2690" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46182,7 +46182,7 @@
       </c>
       <c r="C2691" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46199,7 +46199,7 @@
       </c>
       <c r="C2692" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46318,7 +46318,7 @@
       </c>
       <c r="C2699" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46335,7 +46335,7 @@
       </c>
       <c r="C2700" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46352,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46471,7 +46471,7 @@
       </c>
       <c r="C2708" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46488,7 +46488,7 @@
       </c>
       <c r="C2709" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -46505,7 +46505,7 @@
       </c>
       <c r="C2710" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -47899,7 +47899,7 @@
       </c>
       <c r="C2792" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -47916,7 +47916,7 @@
       </c>
       <c r="C2793" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -47933,7 +47933,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48494,7 +48494,7 @@
       </c>
       <c r="C2827" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6360436466033087</v>
+        <v>0.6423794438577966</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5420679192481518</v>
+        <v>0.5300431783990778</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5739773154052642</v>
+        <v>0.5653858335505969</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6800855582745899</v>
+        <v>0.746111925897337</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5800871843652891</v>
+        <v>0.5809201463089279</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>716.8309399440001</v>
+        <v>1980.514767523</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2523164167349525</v>
+        <v>0.6971188903636044</v>
       </c>
     </row>
   </sheetData>
